--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/125.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/125.xlsx
@@ -426,13 +426,13 @@
         <v>-2.119745645962813</v>
       </c>
       <c r="E2">
-        <v>-21.31380142804662</v>
+        <v>-16.769303604672</v>
       </c>
       <c r="F2">
-        <v>-1.13745545068619</v>
+        <v>-1.376929839896305</v>
       </c>
       <c r="G2">
-        <v>-12.24861316215606</v>
+        <v>-12.06986070149171</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.443090213034035</v>
       </c>
       <c r="E3">
-        <v>-20.78526790806026</v>
+        <v>-18.4057768501489</v>
       </c>
       <c r="F3">
-        <v>-1.498969067513742</v>
+        <v>-0.8710392400674243</v>
       </c>
       <c r="G3">
-        <v>-12.7314886494946</v>
+        <v>-11.76434092646127</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.926228067499879</v>
       </c>
       <c r="E4">
-        <v>-21.24268599053158</v>
+        <v>-18.69885651370807</v>
       </c>
       <c r="F4">
-        <v>-1.585970839094968</v>
+        <v>-1.028125864129906</v>
       </c>
       <c r="G4">
-        <v>-12.65962790462421</v>
+        <v>-11.77493402263971</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.52286280224612</v>
       </c>
       <c r="E5">
-        <v>-21.8319186940303</v>
+        <v>-18.95451574323054</v>
       </c>
       <c r="F5">
-        <v>-1.12065450302261</v>
+        <v>-1.067468345558465</v>
       </c>
       <c r="G5">
-        <v>-12.76120675517524</v>
+        <v>-12.41518911004745</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.206596324473673</v>
       </c>
       <c r="E6">
-        <v>-23.90285106977486</v>
+        <v>-20.61247355089077</v>
       </c>
       <c r="F6">
-        <v>-0.8071547175961237</v>
+        <v>-0.7030496442492957</v>
       </c>
       <c r="G6">
-        <v>-13.09764427302594</v>
+        <v>-13.01587836317686</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.944102267745995</v>
       </c>
       <c r="E7">
-        <v>-24.18129481662534</v>
+        <v>-21.02147764894856</v>
       </c>
       <c r="F7">
-        <v>-1.845832178455382</v>
+        <v>-0.5851969854856073</v>
       </c>
       <c r="G7">
-        <v>-13.30474419846059</v>
+        <v>-13.17828625732854</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.704499052687239</v>
       </c>
       <c r="E8">
-        <v>-24.95946540971316</v>
+        <v>-21.72442527852109</v>
       </c>
       <c r="F8">
-        <v>-0.125278291409891</v>
+        <v>-0.4872259727565098</v>
       </c>
       <c r="G8">
-        <v>-13.29625797316718</v>
+        <v>-13.12780881603166</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.442776047377775</v>
       </c>
       <c r="E9">
-        <v>-25.5835767819178</v>
+        <v>-22.37499260686488</v>
       </c>
       <c r="F9">
-        <v>-0.4732050260967253</v>
+        <v>0.1701075840195791</v>
       </c>
       <c r="G9">
-        <v>-13.43513522631915</v>
+        <v>-13.43657244121656</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.123830231608412</v>
       </c>
       <c r="E10">
-        <v>-26.18624927726367</v>
+        <v>-23.14510596998254</v>
       </c>
       <c r="F10">
-        <v>-0.723636230943669</v>
+        <v>0.1780416870035928</v>
       </c>
       <c r="G10">
-        <v>-14.65323555168406</v>
+        <v>-13.15827751078225</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.717354691324788</v>
       </c>
       <c r="E11">
-        <v>-27.90005116439754</v>
+        <v>-24.48276396706067</v>
       </c>
       <c r="F11">
-        <v>-0.1587517897896162</v>
+        <v>0.5000587460656643</v>
       </c>
       <c r="G11">
-        <v>-12.29435601813695</v>
+        <v>-12.75787152896009</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.193796541163428</v>
       </c>
       <c r="E12">
-        <v>-27.28800071788021</v>
+        <v>-23.68628186524167</v>
       </c>
       <c r="F12">
-        <v>0.7563183439587052</v>
+        <v>0.7913384042794571</v>
       </c>
       <c r="G12">
-        <v>-12.13172490532273</v>
+        <v>-13.0692184859179</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.52961620343201</v>
       </c>
       <c r="E13">
-        <v>-30.94175515520752</v>
+        <v>-26.42730996897937</v>
       </c>
       <c r="F13">
-        <v>0.7535366862201045</v>
+        <v>1.284778642044261</v>
       </c>
       <c r="G13">
-        <v>-13.45827817174708</v>
+        <v>-12.75568894648192</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.720844824674979</v>
       </c>
       <c r="E14">
-        <v>-28.71086599849852</v>
+        <v>-26.21832037511399</v>
       </c>
       <c r="F14">
-        <v>0.7552066749041483</v>
+        <v>1.397708313333112</v>
       </c>
       <c r="G14">
-        <v>-12.37321878000071</v>
+        <v>-12.37488835116673</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.769723224393255</v>
       </c>
       <c r="E15">
-        <v>-31.15901794603195</v>
+        <v>-28.04122089393412</v>
       </c>
       <c r="F15">
-        <v>0.908247552571357</v>
+        <v>1.689041815428087</v>
       </c>
       <c r="G15">
-        <v>-13.11695464539411</v>
+        <v>-12.36907422296232</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.683664791728795</v>
       </c>
       <c r="E16">
-        <v>-31.60743186635104</v>
+        <v>-27.94704059732665</v>
       </c>
       <c r="F16">
-        <v>1.374477577889003</v>
+        <v>1.71799325615593</v>
       </c>
       <c r="G16">
-        <v>-11.04195050884482</v>
+        <v>-10.93676752538575</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.492354979906631</v>
       </c>
       <c r="E17">
-        <v>-31.99104738358015</v>
+        <v>-29.4378773344871</v>
       </c>
       <c r="F17">
-        <v>1.742600738223492</v>
+        <v>2.040282848093522</v>
       </c>
       <c r="G17">
-        <v>-10.57909290565864</v>
+        <v>-10.31385169817989</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.228786422654577</v>
       </c>
       <c r="E18">
-        <v>-32.93718007246103</v>
+        <v>-30.2142703531279</v>
       </c>
       <c r="F18">
-        <v>1.605926743700796</v>
+        <v>2.768537080060291</v>
       </c>
       <c r="G18">
-        <v>-10.49921456414894</v>
+        <v>-9.407616562574127</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.920363860825132</v>
       </c>
       <c r="E19">
-        <v>-33.76645385429521</v>
+        <v>-30.85615331659148</v>
       </c>
       <c r="F19">
-        <v>1.809504659877997</v>
+        <v>2.756881950702902</v>
       </c>
       <c r="G19">
-        <v>-10.04448420887489</v>
+        <v>-9.248053074654464</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.607624322436022</v>
       </c>
       <c r="E20">
-        <v>-36.05810864589778</v>
+        <v>-31.69115645344825</v>
       </c>
       <c r="F20">
-        <v>2.018862923791933</v>
+        <v>3.329626770142119</v>
       </c>
       <c r="G20">
-        <v>-8.973546334621858</v>
+        <v>-8.070543300819891</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.32722824328114</v>
       </c>
       <c r="E21">
-        <v>-35.64589203888023</v>
+        <v>-32.82011142824243</v>
       </c>
       <c r="F21">
-        <v>2.59498085529535</v>
+        <v>3.580365299295501</v>
       </c>
       <c r="G21">
-        <v>-9.439404988715522</v>
+        <v>-8.059943677779971</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.099289401311219</v>
       </c>
       <c r="E22">
-        <v>-35.78246831669156</v>
+        <v>-34.0742234263103</v>
       </c>
       <c r="F22">
-        <v>2.538792694363459</v>
+        <v>3.816431785010499</v>
       </c>
       <c r="G22">
-        <v>-9.28202147252944</v>
+        <v>-7.601379444073878</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.939562301175148</v>
       </c>
       <c r="E23">
-        <v>-37.29555588352478</v>
+        <v>-34.34686513694</v>
       </c>
       <c r="F23">
-        <v>2.574352850230836</v>
+        <v>3.942943368235651</v>
       </c>
       <c r="G23">
-        <v>-7.010121505779861</v>
+        <v>-7.087697170560201</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.863623885669833</v>
       </c>
       <c r="E24">
-        <v>-38.42479535329469</v>
+        <v>-35.53930194683416</v>
       </c>
       <c r="F24">
-        <v>3.82156600617305</v>
+        <v>4.178902166188284</v>
       </c>
       <c r="G24">
-        <v>-7.34851316595701</v>
+        <v>-5.474139529745591</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.86729858159863</v>
       </c>
       <c r="E25">
-        <v>-36.29277131556757</v>
+        <v>-35.84265457860531</v>
       </c>
       <c r="F25">
-        <v>3.484697147946187</v>
+        <v>4.087437151040774</v>
       </c>
       <c r="G25">
-        <v>-7.553869114004798</v>
+        <v>-5.850979625516064</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.933808930072588</v>
       </c>
       <c r="E26">
-        <v>-37.66437350880352</v>
+        <v>-35.86700277999712</v>
       </c>
       <c r="F26">
-        <v>3.303175342235925</v>
+        <v>5.084395544392841</v>
       </c>
       <c r="G26">
-        <v>-6.839605944300479</v>
+        <v>-5.928991284643121</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.059622923187638</v>
       </c>
       <c r="E27">
-        <v>-38.65644486814833</v>
+        <v>-36.1373851436661</v>
       </c>
       <c r="F27">
-        <v>3.262330202338687</v>
+        <v>4.767760388346757</v>
       </c>
       <c r="G27">
-        <v>-8.244941039506259</v>
+        <v>-6.316749514293631</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.225822388332314</v>
       </c>
       <c r="E28">
-        <v>-40.06061446798793</v>
+        <v>-36.65258270208843</v>
       </c>
       <c r="F28">
-        <v>3.705652555499316</v>
+        <v>4.285141942332126</v>
       </c>
       <c r="G28">
-        <v>-7.071648923558628</v>
+        <v>-6.664127357353391</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.404011534670781</v>
       </c>
       <c r="E29">
-        <v>-39.02441108510549</v>
+        <v>-36.65370822235746</v>
       </c>
       <c r="F29">
-        <v>3.273650671265345</v>
+        <v>4.281536887395143</v>
       </c>
       <c r="G29">
-        <v>-7.366388934172362</v>
+        <v>-5.585667927933359</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.584951944655639</v>
       </c>
       <c r="E30">
-        <v>-39.530405127232</v>
+        <v>-36.2618631168882</v>
       </c>
       <c r="F30">
-        <v>3.001513755362846</v>
+        <v>4.056775959993553</v>
       </c>
       <c r="G30">
-        <v>-7.261123712258675</v>
+        <v>-6.726735623392878</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.754063345501901</v>
       </c>
       <c r="E31">
-        <v>-40.43227704302418</v>
+        <v>-35.99409519974819</v>
       </c>
       <c r="F31">
-        <v>3.309518979806564</v>
+        <v>3.918993609885911</v>
       </c>
       <c r="G31">
-        <v>-7.176908923983134</v>
+        <v>-5.6162971834763</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.889235644804283</v>
       </c>
       <c r="E32">
-        <v>-37.63452022580066</v>
+        <v>-35.80577198543516</v>
       </c>
       <c r="F32">
-        <v>2.195151104251306</v>
+        <v>3.429521251980517</v>
       </c>
       <c r="G32">
-        <v>-8.6720562438678</v>
+        <v>-6.468467714716996</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.983551669440627</v>
       </c>
       <c r="E33">
-        <v>-37.23820211173456</v>
+        <v>-35.71113898879329</v>
       </c>
       <c r="F33">
-        <v>2.786461293922066</v>
+        <v>3.328400786385976</v>
       </c>
       <c r="G33">
-        <v>-6.941330996548617</v>
+        <v>-6.079970644347202</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.032607043159363</v>
       </c>
       <c r="E34">
-        <v>-38.0367919683009</v>
+        <v>-35.4782601233875</v>
       </c>
       <c r="F34">
-        <v>2.643070896497472</v>
+        <v>3.45245708862923</v>
       </c>
       <c r="G34">
-        <v>-5.894477241148603</v>
+        <v>-6.673228412998012</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.026985200126029</v>
       </c>
       <c r="E35">
-        <v>-37.35566738763468</v>
+        <v>-34.5589301837914</v>
       </c>
       <c r="F35">
-        <v>2.060720328655392</v>
+        <v>3.437576296605339</v>
       </c>
       <c r="G35">
-        <v>-6.86198002544632</v>
+        <v>-5.555213592278022</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.962916408906509</v>
       </c>
       <c r="E36">
-        <v>-38.3569152674017</v>
+        <v>-34.65143881284063</v>
       </c>
       <c r="F36">
-        <v>1.912440906819475</v>
+        <v>2.739285770332635</v>
       </c>
       <c r="G36">
-        <v>-6.730690901448415</v>
+        <v>-5.850715940312362</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.847047586987735</v>
       </c>
       <c r="E37">
-        <v>-36.25392217683513</v>
+        <v>-33.78070352235069</v>
       </c>
       <c r="F37">
-        <v>1.607939676489599</v>
+        <v>2.680821255777851</v>
       </c>
       <c r="G37">
-        <v>-7.41201691739125</v>
+        <v>-5.407147823537624</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.679825070225121</v>
       </c>
       <c r="E38">
-        <v>-37.43108139887092</v>
+        <v>-33.17705086913217</v>
       </c>
       <c r="F38">
-        <v>1.689122995433561</v>
+        <v>2.638521502721297</v>
       </c>
       <c r="G38">
-        <v>-5.987093405518347</v>
+        <v>-5.569029652654194</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.459712176333801</v>
       </c>
       <c r="E39">
-        <v>-38.01804644898628</v>
+        <v>-32.78079505323593</v>
       </c>
       <c r="F39">
-        <v>1.530248754515839</v>
+        <v>2.148197583125825</v>
       </c>
       <c r="G39">
-        <v>-6.883356802158356</v>
+        <v>-5.620946919593073</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.200614313157549</v>
       </c>
       <c r="E40">
-        <v>-36.21914526180667</v>
+        <v>-32.12060058104119</v>
       </c>
       <c r="F40">
-        <v>1.872263431048893</v>
+        <v>2.273859261395704</v>
       </c>
       <c r="G40">
-        <v>-6.379587525857136</v>
+        <v>-5.156798303206588</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.908634788234172</v>
       </c>
       <c r="E41">
-        <v>-34.35929154522388</v>
+        <v>-32.88007964656163</v>
       </c>
       <c r="F41">
-        <v>1.444191321773804</v>
+        <v>2.012139893950812</v>
       </c>
       <c r="G41">
-        <v>-4.929146596350692</v>
+        <v>-4.897091874261003</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.584153263159608</v>
       </c>
       <c r="E42">
-        <v>-33.56892089386938</v>
+        <v>-32.00765607566814</v>
       </c>
       <c r="F42">
-        <v>1.252512074970415</v>
+        <v>1.974086352201008</v>
       </c>
       <c r="G42">
-        <v>-5.98906973917382</v>
+        <v>-4.443057282420492</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.239089268763116</v>
       </c>
       <c r="E43">
-        <v>-33.7526859587534</v>
+        <v>-31.17879553836078</v>
       </c>
       <c r="F43">
-        <v>1.127909050241313</v>
+        <v>1.864579495020525</v>
       </c>
       <c r="G43">
-        <v>-5.564708870355902</v>
+        <v>-4.734197076243081</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.880288181619539</v>
       </c>
       <c r="E44">
-        <v>-34.03901250069841</v>
+        <v>-31.38255208595687</v>
       </c>
       <c r="F44">
-        <v>1.981044638384524</v>
+        <v>1.569574668596342</v>
       </c>
       <c r="G44">
-        <v>-5.316886550789064</v>
+        <v>-4.459306556755581</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.506837232588413</v>
       </c>
       <c r="E45">
-        <v>-34.31214429026443</v>
+        <v>-30.9701548142467</v>
       </c>
       <c r="F45">
-        <v>1.458303388847896</v>
+        <v>2.119541041193379</v>
       </c>
       <c r="G45">
-        <v>-5.069523722270262</v>
+        <v>-5.15527884985456</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.124227765744434</v>
       </c>
       <c r="E46">
-        <v>-33.8504670895795</v>
+        <v>-31.16442750378254</v>
       </c>
       <c r="F46">
-        <v>1.759222758528067</v>
+        <v>1.57806046427062</v>
       </c>
       <c r="G46">
-        <v>-5.726144262147391</v>
+        <v>-4.128493888126434</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.739685334736553</v>
       </c>
       <c r="E47">
-        <v>-32.82281101560356</v>
+        <v>-29.61170584127648</v>
       </c>
       <c r="F47">
-        <v>1.412594075561419</v>
+        <v>1.717227844675743</v>
       </c>
       <c r="G47">
-        <v>-4.69674333433897</v>
+        <v>-3.95663640392722</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.355137887574823</v>
       </c>
       <c r="E48">
-        <v>-32.85202470406241</v>
+        <v>-29.34931010298514</v>
       </c>
       <c r="F48">
-        <v>0.6193453088035986</v>
+        <v>1.755470254193385</v>
       </c>
       <c r="G48">
-        <v>-6.533480476524899</v>
+        <v>-4.373162428227207</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.974738588457474</v>
       </c>
       <c r="E49">
-        <v>-32.70396272033227</v>
+        <v>-28.6244231345892</v>
       </c>
       <c r="F49">
-        <v>0.7420538572824977</v>
+        <v>1.504809591575866</v>
       </c>
       <c r="G49">
-        <v>-5.093150960819838</v>
+        <v>-4.429371759273875</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.61181258195826</v>
       </c>
       <c r="E50">
-        <v>-31.78981598846956</v>
+        <v>-28.69576284551578</v>
       </c>
       <c r="F50">
-        <v>0.8908617775214009</v>
+        <v>1.513474314609148</v>
       </c>
       <c r="G50">
-        <v>-5.423337050747117</v>
+        <v>-4.40790099575656</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.272811516572142</v>
       </c>
       <c r="E51">
-        <v>-31.23848133830989</v>
+        <v>-26.93338707533237</v>
       </c>
       <c r="F51">
-        <v>1.032613664223258</v>
+        <v>1.522760313194531</v>
       </c>
       <c r="G51">
-        <v>-5.265723789037017</v>
+        <v>-4.792581157534148</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.960680840990764</v>
       </c>
       <c r="E52">
-        <v>-31.1134011494457</v>
+        <v>-27.51344948822588</v>
       </c>
       <c r="F52">
-        <v>0.8887726349315406</v>
+        <v>1.432604118543444</v>
       </c>
       <c r="G52">
-        <v>-4.33858050537332</v>
+        <v>-4.471553559632493</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.688594826071589</v>
       </c>
       <c r="E53">
-        <v>-28.95325156462684</v>
+        <v>-26.76771132237364</v>
       </c>
       <c r="F53">
-        <v>0.9303003495686855</v>
+        <v>1.528944904223832</v>
       </c>
       <c r="G53">
-        <v>-6.17297058817184</v>
+        <v>-4.496193767083421</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.461687475546805</v>
       </c>
       <c r="E54">
-        <v>-29.91739050120651</v>
+        <v>-26.33696100981905</v>
       </c>
       <c r="F54">
-        <v>0.5439729871902744</v>
+        <v>1.121239035913971</v>
       </c>
       <c r="G54">
-        <v>-5.017120856837437</v>
+        <v>-4.245554454102772</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.279112063255817</v>
       </c>
       <c r="E55">
-        <v>-28.71539299884258</v>
+        <v>-25.17203091852921</v>
       </c>
       <c r="F55">
-        <v>0.6457354375219853</v>
+        <v>0.8475033709240692</v>
       </c>
       <c r="G55">
-        <v>-4.97674569173587</v>
+        <v>-5.140235739520565</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.146885429275839</v>
       </c>
       <c r="E56">
-        <v>-27.54633876870719</v>
+        <v>-24.92233985368052</v>
       </c>
       <c r="F56">
-        <v>0.2667159323710714</v>
+        <v>1.171903643003995</v>
       </c>
       <c r="G56">
-        <v>-6.162504113106066</v>
+        <v>-4.930514626516436</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.065953889734039</v>
       </c>
       <c r="E57">
-        <v>-28.16227039120758</v>
+        <v>-24.20994782155533</v>
       </c>
       <c r="F57">
-        <v>0.7468567314839293</v>
+        <v>0.804221174127795</v>
       </c>
       <c r="G57">
-        <v>-4.534947659793906</v>
+        <v>-5.245696767278587</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.030254151812124</v>
       </c>
       <c r="E58">
-        <v>-26.86472203249898</v>
+        <v>-24.76726724923407</v>
       </c>
       <c r="F58">
-        <v>0.9690348093235903</v>
+        <v>0.8736516163608384</v>
       </c>
       <c r="G58">
-        <v>-5.951840521304544</v>
+        <v>-5.699632150824636</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.036482277025912</v>
       </c>
       <c r="E59">
-        <v>-26.049841204511</v>
+        <v>-23.66697358579255</v>
       </c>
       <c r="F59">
-        <v>0.2032638176840321</v>
+        <v>0.6262083327357925</v>
       </c>
       <c r="G59">
-        <v>-5.84508195348474</v>
+        <v>-5.886558852803756</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.080256484508048</v>
       </c>
       <c r="E60">
-        <v>-25.82661440222411</v>
+        <v>-23.22963212686545</v>
       </c>
       <c r="F60">
-        <v>-0.2938866776779108</v>
+        <v>0.8319002425249378</v>
       </c>
       <c r="G60">
-        <v>-5.69077650517158</v>
+        <v>-5.762543263236693</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.150557577620228</v>
       </c>
       <c r="E61">
-        <v>-27.89954447261591</v>
+        <v>-22.57800988284515</v>
       </c>
       <c r="F61">
-        <v>0.6480043358382531</v>
+        <v>0.1623739459470429</v>
       </c>
       <c r="G61">
-        <v>-7.215391299256143</v>
+        <v>-6.060089824285874</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.235014448640174</v>
       </c>
       <c r="E62">
-        <v>-27.79184754975178</v>
+        <v>-22.33362662206959</v>
       </c>
       <c r="F62">
-        <v>0.3013524585843272</v>
+        <v>0.4372411608091693</v>
       </c>
       <c r="G62">
-        <v>-6.733092786472239</v>
+        <v>-6.46008200309034</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.323644968538685</v>
       </c>
       <c r="E63">
-        <v>-25.50016783888126</v>
+        <v>-20.6530421191117</v>
       </c>
       <c r="F63">
-        <v>0.1065080199348415</v>
+        <v>-0.3753690372542841</v>
       </c>
       <c r="G63">
-        <v>-6.85377184445186</v>
+        <v>-6.685209119926631</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.401684817477745</v>
       </c>
       <c r="E64">
-        <v>-24.71589202514594</v>
+        <v>-21.22299976885189</v>
       </c>
       <c r="F64">
-        <v>0.1235259998579545</v>
+        <v>-0.3080559021027963</v>
       </c>
       <c r="G64">
-        <v>-6.481338685551185</v>
+        <v>-7.556620838803831</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.453607487942125</v>
       </c>
       <c r="E65">
-        <v>-22.50262909729951</v>
+        <v>-20.81519179565565</v>
       </c>
       <c r="F65">
-        <v>-0.1063749472780063</v>
+        <v>-0.2064466997406033</v>
       </c>
       <c r="G65">
-        <v>-8.675806578472935</v>
+        <v>-7.204157265280583</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.469073876053034</v>
       </c>
       <c r="E66">
-        <v>-24.66111947419411</v>
+        <v>-21.07180626378283</v>
       </c>
       <c r="F66">
-        <v>-0.6292048321267338</v>
+        <v>-0.5223421236959864</v>
       </c>
       <c r="G66">
-        <v>-7.511760414494733</v>
+        <v>-6.722529713856595</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.437524512800369</v>
       </c>
       <c r="E67">
-        <v>-25.81853640619732</v>
+        <v>-20.20497706854389</v>
       </c>
       <c r="F67">
-        <v>-0.8202644601128286</v>
+        <v>-0.545728592211822</v>
       </c>
       <c r="G67">
-        <v>-7.007074766842032</v>
+        <v>-6.883009573127738</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.3509647899603</v>
       </c>
       <c r="E68">
-        <v>-25.59636036637562</v>
+        <v>-20.84362883359675</v>
       </c>
       <c r="F68">
-        <v>-0.4970628356647539</v>
+        <v>-0.5209943699316316</v>
       </c>
       <c r="G68">
-        <v>-8.156058239901807</v>
+        <v>-7.51348872741405</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.20608520628213</v>
       </c>
       <c r="E69">
-        <v>-22.99698168808253</v>
+        <v>-20.14370058865737</v>
       </c>
       <c r="F69">
-        <v>-0.6202584641764992</v>
+        <v>-1.399140026700165</v>
       </c>
       <c r="G69">
-        <v>-7.397587332036166</v>
+        <v>-7.379565362123711</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.002657060998185</v>
       </c>
       <c r="E70">
-        <v>-24.73056947396789</v>
+        <v>-20.04399029117089</v>
       </c>
       <c r="F70">
-        <v>-1.21440664056925</v>
+        <v>-1.188471285555</v>
       </c>
       <c r="G70">
-        <v>-7.975324224092807</v>
+        <v>-6.768079374737749</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.74436380066715</v>
       </c>
       <c r="E71">
-        <v>-24.45303943360887</v>
+        <v>-19.76741133620526</v>
       </c>
       <c r="F71">
-        <v>-0.5948698316480971</v>
+        <v>-1.362804518943768</v>
       </c>
       <c r="G71">
-        <v>-7.339887265827971</v>
+        <v>-7.283949452218778</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.437797871609694</v>
       </c>
       <c r="E72">
-        <v>-25.10255599948748</v>
+        <v>-19.72485753297106</v>
       </c>
       <c r="F72">
-        <v>-1.342562533088959</v>
+        <v>-1.285143418196508</v>
       </c>
       <c r="G72">
-        <v>-7.225082383178355</v>
+        <v>-7.0042342767269</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.092206928906606</v>
       </c>
       <c r="E73">
-        <v>-25.61980524430428</v>
+        <v>-19.64705957843438</v>
       </c>
       <c r="F73">
-        <v>-1.638580452846765</v>
+        <v>-1.266788453285277</v>
       </c>
       <c r="G73">
-        <v>-6.204469221663621</v>
+        <v>-6.710927564893687</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.7177604970327078</v>
       </c>
       <c r="E74">
-        <v>-24.72427320559945</v>
+        <v>-21.05911404997416</v>
       </c>
       <c r="F74">
-        <v>-1.917411405731287</v>
+        <v>-1.4928018721999</v>
       </c>
       <c r="G74">
-        <v>-6.77779134461669</v>
+        <v>-6.080302208910274</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3231515575180812</v>
       </c>
       <c r="E75">
-        <v>-24.167622444944</v>
+        <v>-20.51826210519836</v>
       </c>
       <c r="F75">
-        <v>-1.059213664389568</v>
+        <v>-1.626097784453979</v>
       </c>
       <c r="G75">
-        <v>-5.706083300709277</v>
+        <v>-5.918297674797921</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.08362207164462747</v>
       </c>
       <c r="E76">
-        <v>-24.74913432858987</v>
+        <v>-20.92088687066121</v>
       </c>
       <c r="F76">
-        <v>-2.139868643385691</v>
+        <v>-2.031805630588288</v>
       </c>
       <c r="G76">
-        <v>-5.277824590216827</v>
+        <v>-5.50989889841007</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.496425422448962</v>
       </c>
       <c r="E77">
-        <v>-24.11201509851587</v>
+        <v>-21.41631098996604</v>
       </c>
       <c r="F77">
-        <v>-1.742832975591291</v>
+        <v>-2.05098647780011</v>
       </c>
       <c r="G77">
-        <v>-6.121541530471498</v>
+        <v>-4.876560978796489</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.9087729929172016</v>
       </c>
       <c r="E78">
-        <v>-24.75035537271937</v>
+        <v>-21.53163736203387</v>
       </c>
       <c r="F78">
-        <v>-1.542643910458943</v>
+        <v>-1.800628169284613</v>
       </c>
       <c r="G78">
-        <v>-4.644173381252313</v>
+        <v>-5.013674673977167</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.314510775482202</v>
       </c>
       <c r="E79">
-        <v>-25.02805984795403</v>
+        <v>-22.34967463062873</v>
       </c>
       <c r="F79">
-        <v>-2.358965194486938</v>
+        <v>-2.148976542979472</v>
       </c>
       <c r="G79">
-        <v>-3.898163557320056</v>
+        <v>-4.311653285660578</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.707606050701346</v>
       </c>
       <c r="E80">
-        <v>-26.12224413753673</v>
+        <v>-22.1941700922045</v>
       </c>
       <c r="F80">
-        <v>-1.42791751027342</v>
+        <v>-2.392030307737083</v>
       </c>
       <c r="G80">
-        <v>-4.830403014425605</v>
+        <v>-4.121721616657086</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.079647752586566</v>
       </c>
       <c r="E81">
-        <v>-28.61667116565141</v>
+        <v>-22.920899009823</v>
       </c>
       <c r="F81">
-        <v>-2.018101120276373</v>
+        <v>-2.138245043276204</v>
       </c>
       <c r="G81">
-        <v>-3.990745782010115</v>
+        <v>-3.535729550203345</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.42503606706766</v>
       </c>
       <c r="E82">
-        <v>-27.11072504569123</v>
+        <v>-23.89314916812006</v>
       </c>
       <c r="F82">
-        <v>-2.357783114203143</v>
+        <v>-1.968880357569429</v>
       </c>
       <c r="G82">
-        <v>-4.327983493077991</v>
+        <v>-3.082512121419852</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.7369209431211</v>
       </c>
       <c r="E83">
-        <v>-27.88378718884951</v>
+        <v>-25.48760852783498</v>
       </c>
       <c r="F83">
-        <v>-2.374564181049056</v>
+        <v>-2.199512753122062</v>
       </c>
       <c r="G83">
-        <v>-2.808443986478552</v>
+        <v>-2.603168971513088</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.007236516878724</v>
       </c>
       <c r="E84">
-        <v>-30.56496751739642</v>
+        <v>-25.81512246648831</v>
       </c>
       <c r="F84">
-        <v>-2.098937353278562</v>
+        <v>-2.008984108641161</v>
       </c>
       <c r="G84">
-        <v>-3.222583790222262</v>
+        <v>-2.712441686374135</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.228932282340714</v>
       </c>
       <c r="E85">
-        <v>-31.19412504136072</v>
+        <v>-27.10551691868989</v>
       </c>
       <c r="F85">
-        <v>-1.622809994232268</v>
+        <v>-2.140650622213934</v>
       </c>
       <c r="G85">
-        <v>-3.27822920043725</v>
+        <v>-2.997114665844536</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.394195859485538</v>
       </c>
       <c r="E86">
-        <v>-31.03191514325256</v>
+        <v>-27.9386178847599</v>
       </c>
       <c r="F86">
-        <v>-2.106020722939901</v>
+        <v>-2.151305912116144</v>
       </c>
       <c r="G86">
-        <v>-2.682616540165256</v>
+        <v>-2.000776207537973</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.494762844714708</v>
       </c>
       <c r="E87">
-        <v>-30.84921745367901</v>
+        <v>-29.9696462060955</v>
       </c>
       <c r="F87">
-        <v>-1.967066232957298</v>
+        <v>-2.131605678542766</v>
       </c>
       <c r="G87">
-        <v>-2.645486530590443</v>
+        <v>-2.061094850571054</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.523603537415521</v>
       </c>
       <c r="E88">
-        <v>-32.49127261517648</v>
+        <v>-31.06018605274067</v>
       </c>
       <c r="F88">
-        <v>-2.404913905952824</v>
+        <v>-2.105910550075329</v>
       </c>
       <c r="G88">
-        <v>-3.678325809025361</v>
+        <v>-2.187987480677525</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.476317613598226</v>
       </c>
       <c r="E89">
-        <v>-33.59090384141169</v>
+        <v>-32.13879164664394</v>
       </c>
       <c r="F89">
-        <v>-2.444460994129875</v>
+        <v>-1.802062901626261</v>
       </c>
       <c r="G89">
-        <v>-3.108541244993251</v>
+        <v>-2.0034417777655</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.349785935950783</v>
       </c>
       <c r="E90">
-        <v>-36.1791872156505</v>
+        <v>-34.48884681929059</v>
       </c>
       <c r="F90">
-        <v>-1.934716829143172</v>
+        <v>-1.853697526944963</v>
       </c>
       <c r="G90">
-        <v>-2.450513513781512</v>
+        <v>-1.82423243679771</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.143029837409637</v>
       </c>
       <c r="E91">
-        <v>-36.6973647031984</v>
+        <v>-35.30543669373873</v>
       </c>
       <c r="F91">
-        <v>-2.482008403396569</v>
+        <v>-1.939055817599035</v>
       </c>
       <c r="G91">
-        <v>-3.284711679256985</v>
+        <v>-2.534088669632231</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.857381777431778</v>
       </c>
       <c r="E92">
-        <v>-38.30471563086559</v>
+        <v>-36.33664999321439</v>
       </c>
       <c r="F92">
-        <v>-2.0204172355346</v>
+        <v>-1.833452227620543</v>
       </c>
       <c r="G92">
-        <v>-3.414627551599964</v>
+        <v>-2.404316388241762</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.495056119209281</v>
       </c>
       <c r="E93">
-        <v>-40.3431138256971</v>
+        <v>-39.26718289988702</v>
       </c>
       <c r="F93">
-        <v>-1.734208014193343</v>
+        <v>-1.560638535549957</v>
       </c>
       <c r="G93">
-        <v>-4.165195735588305</v>
+        <v>-2.472814494078801</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.061658482737859</v>
       </c>
       <c r="E94">
-        <v>-41.15242104408716</v>
+        <v>-40.17021356163882</v>
       </c>
       <c r="F94">
-        <v>-1.639125518597807</v>
+        <v>-1.434768108694572</v>
       </c>
       <c r="G94">
-        <v>-3.259690303095755</v>
+        <v>-2.717509141625485</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.564803870370353</v>
       </c>
       <c r="E95">
-        <v>-41.14948057046919</v>
+        <v>-42.79217740311633</v>
       </c>
       <c r="F95">
-        <v>-2.724566804447305</v>
+        <v>-1.024032900792673</v>
       </c>
       <c r="G95">
-        <v>-4.526624606037437</v>
+        <v>-3.455013159679895</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.009026004004592</v>
       </c>
       <c r="E96">
-        <v>-46.0792302763349</v>
+        <v>-44.53616067694774</v>
       </c>
       <c r="F96">
-        <v>-2.660400637059053</v>
+        <v>-0.984771599369588</v>
       </c>
       <c r="G96">
-        <v>-4.419262956217085</v>
+        <v>-2.92836592852675</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.4119274407042948</v>
       </c>
       <c r="E97">
-        <v>-47.92651533714592</v>
+        <v>-45.62784577161572</v>
       </c>
       <c r="F97">
-        <v>-2.112742096046216</v>
+        <v>-0.6798851781974103</v>
       </c>
       <c r="G97">
-        <v>-4.580314568553682</v>
+        <v>-3.879473236792276</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2283493037772414</v>
       </c>
       <c r="E98">
-        <v>-49.13638421327323</v>
+        <v>-48.48102615566625</v>
       </c>
       <c r="F98">
-        <v>-1.350793191603175</v>
+        <v>-0.5974477110056092</v>
       </c>
       <c r="G98">
-        <v>-5.603721226780907</v>
+        <v>-4.593772956920871</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.8796728480649373</v>
       </c>
       <c r="E99">
-        <v>-50.71336374482479</v>
+        <v>-50.72665505936707</v>
       </c>
       <c r="F99">
-        <v>-1.159183527661621</v>
+        <v>-0.4647473949141424</v>
       </c>
       <c r="G99">
-        <v>-6.694537310350678</v>
+        <v>-4.05426258716731</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.559950054240013</v>
       </c>
       <c r="E100">
-        <v>-52.68786789833231</v>
+        <v>-51.83605463863828</v>
       </c>
       <c r="F100">
-        <v>-1.153911797510205</v>
+        <v>-0.1687659233220594</v>
       </c>
       <c r="G100">
-        <v>-5.756423677915124</v>
+        <v>-5.312072337763051</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.209166676083556</v>
       </c>
       <c r="E101">
-        <v>-53.25088553194871</v>
+        <v>-54.92236723398541</v>
       </c>
       <c r="F101">
-        <v>-0.3549265864879979</v>
+        <v>0.133510312163897</v>
       </c>
       <c r="G101">
-        <v>-6.744880298301116</v>
+        <v>-5.058602977645635</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.895083792569375</v>
       </c>
       <c r="E102">
-        <v>-56.96136868276186</v>
+        <v>-56.68304849394829</v>
       </c>
       <c r="F102">
-        <v>-1.093900721014395</v>
+        <v>0.5709181220685368</v>
       </c>
       <c r="G102">
-        <v>-5.896996609679027</v>
+        <v>-5.941076421355384</v>
       </c>
     </row>
   </sheetData>
